--- a/static/standards-correlations/South_Dakota_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/South_Dakota_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$19</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | SD CTE Information Technology cluster - NOT a 9-12 CS standards band</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | SD CTE Information Technology cluster - NOT a 9-12 CS standards band</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -659,7 +660,7 @@
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>PreLab 1 (The Toolchain) boots the controller and runs a program the student typed. Unit 3.3 is the strongest evidence: students switch the KIPR IDE to Advanced mode to see source and header files as separate things, create a header-file library, and include it with #include - software structure as a stated objective with a work product. Ext 3.1E (Computer vs. Peripheral) separates the processor running the program from the memory holding it, and Ext 3.1F (Compiled, Typed, and Running on Something) contrasts compiled against interpreted execution. Discovery Systems 8 asks where meaning is lost between software, translator, and hardware.</t>
+          <t>PreLab 1 (The Toolchain) boots the controller and runs a program the student typed. Unit 3.3 is the strongest evidence: students switch the KIPR IDE to Advanced mode to see source and header files as separate things, create a header-file library, and include it with #include - software structure as a stated objective with a work product. Ext 3.1E (Computer vs. Peripheral) separates the processor running the program from the memory holding it, and Ext 3.1F (Compiled, Typed, and Running on Something) contrasts compiled against interpreted execution. Introductory Systems 8 asks where meaning is lost between software, translator, and hardware.</t>
         </is>
       </c>
     </row>
@@ -706,7 +707,7 @@
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Execute and debug are continuous, not occasional: Unit 1.1 carries 'use a structured debugging process to find and fix errors in your code' as a stated objective, and 64 prompts across the two tracks and the Discovery strand require students to describe a bug's symptom, cause, and fix. Units 1.3, 1.4, 1.5, and 2.3 each carry a dedicated common-bugs callout. Compilation is named explicitly in Ext 3.1F (Compiled, Typed, and Running on Something). Discovery Coding 2 notes that professional programmers spend most of their working time debugging.</t>
+          <t>Execute and debug are continuous, not occasional: Unit 1.1 carries 'use a structured debugging process to find and fix errors in your code' as a stated objective, and 64 prompts across the two tracks and the Introductory strand require students to describe a bug's symptom, cause, and fix. Units 1.3, 1.4, 1.5, and 2.3 each carry a dedicated common-bugs callout. Compilation is named explicitly in Ext 3.1F (Compiled, Typed, and Running on Something). Introductory Coding 2 notes that professional programmers spend most of their working time debugging.</t>
         </is>
       </c>
     </row>
@@ -847,7 +848,7 @@
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>Scored on the specific syntactic elements the labs name and require students to explain, not on a standalone syntax lesson. Unit 1.5 requires writing a function prototype and explaining why it comes before main(). Unit 4.3 asks how 'R' differs from "R" and why a char must use single quotes, backed by a dedicated Single quotes, not double callout. Unit 3.3 covers #include and the source-versus-header split. Discovery Coding 2 asks why line 1 carries a # and no semicolon when every other line differs. NOTE: South Dakota writes this at Recall level; the curriculum meets it through embedded, repeated use rather than a dedicated syntax unit.</t>
+          <t>Scored on the specific syntactic elements the labs name and require students to explain, not on a standalone syntax lesson. Unit 1.5 requires writing a function prototype and explaining why it comes before main(). Unit 4.3 asks how 'R' differs from "R" and why a char must use single quotes, backed by a dedicated Single quotes, not double callout. Unit 3.3 covers #include and the source-versus-header split. Introductory Coding 2 asks why line 1 carries a # and no semicolon when every other line differs. NOTE: South Dakota writes this at Recall level; the curriculum meets it through embedded, repeated use rather than a dedicated syntax unit.</t>
         </is>
       </c>
     </row>
@@ -1331,6 +1332,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1375,7 +1377,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1389,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -1499,6 +1501,8 @@
         </is>
       </c>
     </row>
+    <row r="17"/>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
@@ -1522,7 +1526,7 @@
 PAGINATION QUIRK IN SOURCE: the PDF header reads 'Adopted March 2021' while the standards pages carry a running footer reading 'Proposed 2020-2021'. Treat March 2021 as the adoption date; verify with SD DOE CTE before any formal submission. Contact: Tracia Rentsch, (605) 220-6612.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.
 RESULT SHAPE - READ BEFORE PRESENTING: 13 Full, 1 Partial, 1 blank of 15. This is the highest Full rate in the series and it is concentrated entirely in indicators 1 through 4, which are programming-mechanics indicators that a programming curriculum should hit. The whole of the shortfall is indicator CP 5, careers - which this curriculum genuinely does not teach. Present the CP 5 gap openly. A file showing 15/15 would be less credible than this one, and the honest gap points a district at the cluster's own foundational courses, which is where South Dakota already puts career exploration.</t>
         </is>
